--- a/Demo/ONCHO/ento/river prospection/demo_oncho_priv_prosp_9999_2_community.xlsx
+++ b/Demo/ONCHO/ento/river prospection/demo_oncho_priv_prosp_9999_2_community.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\ONCHO\ento\river prospection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634F42DF-0E69-42E0-BBC8-A78194CB8E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5B6A9F-9160-4A82-8F8C-32B6BFF8A887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="252">
   <si>
     <t>type</t>
   </si>
@@ -788,6 +788,9 @@
   </si>
   <si>
     <t>99 (For testing only)</t>
+  </si>
+  <si>
+    <t>Do not know</t>
   </si>
 </sst>
 </file>
@@ -889,7 +892,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -936,10 +939,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -948,6 +947,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1664,7 +1665,7 @@
       <c r="L16" s="6"/>
       <c r="M16" s="5"/>
     </row>
-    <row r="17" spans="1:13" s="4" customFormat="1">
+    <row r="17" spans="1:13" s="4" customFormat="1" ht="31.5">
       <c r="A17" s="5" t="s">
         <v>236</v>
       </c>
@@ -1866,9 +1867,10 @@
   <dimension ref="A1:G420"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="16.375" customWidth="1"/>
-    <col min="2" max="2" width="18.75" customWidth="1"/>
-    <col min="3" max="3" width="17.5" customWidth="1"/>
+    <col min="1" max="1" width="16.375" style="10" customWidth="1"/>
+    <col min="2" max="2" width="18.75" style="10" customWidth="1"/>
+    <col min="3" max="3" width="17.5" style="10" customWidth="1"/>
+    <col min="4" max="16384" width="11" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1894,500 +1896,500 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="10" customFormat="1">
+    <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="23" t="s">
         <v>240</v>
       </c>
       <c r="E2" s="3"/>
-      <c r="F2" s="25"/>
+      <c r="F2" s="21"/>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" s="10" customFormat="1">
+    <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="23" t="s">
         <v>241</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="25"/>
+      <c r="F3" s="21"/>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7" s="10" customFormat="1">
+    <row r="4" spans="1:7">
       <c r="A4" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="23" t="s">
         <v>242</v>
       </c>
       <c r="E4" s="3"/>
-      <c r="F4" s="25"/>
+      <c r="F4" s="21"/>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" s="10" customFormat="1">
+    <row r="5" spans="1:7">
       <c r="A5" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="23" t="s">
         <v>243</v>
       </c>
       <c r="E5" s="3"/>
-      <c r="F5" s="25"/>
+      <c r="F5" s="21"/>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:7" s="10" customFormat="1">
+    <row r="6" spans="1:7">
       <c r="A6" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="23" t="s">
         <v>244</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="25"/>
+      <c r="F6" s="21"/>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:7" s="10" customFormat="1">
+    <row r="7" spans="1:7">
       <c r="A7" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="23" t="s">
         <v>245</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="25"/>
+      <c r="F7" s="21"/>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:7" s="10" customFormat="1">
+    <row r="8" spans="1:7">
       <c r="A8" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="23" t="s">
         <v>246</v>
       </c>
       <c r="E8" s="3"/>
-      <c r="F8" s="25"/>
+      <c r="F8" s="21"/>
       <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:7" s="10" customFormat="1">
+    <row r="9" spans="1:7">
       <c r="A9" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="23" t="s">
         <v>247</v>
       </c>
       <c r="E9" s="3"/>
-      <c r="F9" s="25"/>
+      <c r="F9" s="21"/>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:7" s="10" customFormat="1">
+    <row r="10" spans="1:7">
       <c r="A10" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="23" t="s">
         <v>248</v>
       </c>
       <c r="E10" s="3"/>
-      <c r="F10" s="25"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" s="10" customFormat="1">
+    <row r="11" spans="1:7">
       <c r="A11" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="23" t="s">
         <v>249</v>
       </c>
       <c r="E11" s="3"/>
-      <c r="F11" s="25"/>
+      <c r="F11" s="21"/>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:7" s="10" customFormat="1">
-      <c r="A12" s="26" t="s">
+    <row r="12" spans="1:7">
+      <c r="A12" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="20">
         <v>99</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="23" t="s">
         <v>250</v>
       </c>
       <c r="E12" s="3"/>
-      <c r="F12" s="25"/>
+      <c r="F12" s="21"/>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="C19" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="C19" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="24" t="s">
         <v>221</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="24" t="s">
         <v>222</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="25" t="s">
         <v>224</v>
       </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="24" t="s">
         <v>226</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="25" t="s">
         <v>226</v>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="24" t="s">
         <v>227</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="25" t="s">
         <v>227</v>
       </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="22" t="s">
+      <c r="B30" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="C31" s="25" t="s">
         <v>229</v>
       </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="20" t="s">
+      <c r="A32" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="24" t="s">
         <v>230</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="20" t="s">
+      <c r="A33" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C33" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="24" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="23" t="s">
+      <c r="C34" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="20"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-    </row>
-    <row r="36" spans="1:7" s="10" customFormat="1">
+      <c r="A35" s="16"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" s="16" t="s">
         <v>40</v>
       </c>
@@ -2402,7 +2404,7 @@
       <c r="F36" s="16"/>
       <c r="G36" s="16"/>
     </row>
-    <row r="37" spans="1:7" s="10" customFormat="1">
+    <row r="37" spans="1:7">
       <c r="A37" s="16" t="s">
         <v>40</v>
       </c>
@@ -2417,7 +2419,7 @@
       <c r="F37" s="16"/>
       <c r="G37" s="16"/>
     </row>
-    <row r="38" spans="1:7" s="10" customFormat="1">
+    <row r="38" spans="1:7">
       <c r="A38" s="16" t="s">
         <v>40</v>
       </c>
@@ -2432,7 +2434,7 @@
       <c r="F38" s="16"/>
       <c r="G38" s="16"/>
     </row>
-    <row r="39" spans="1:7" s="10" customFormat="1">
+    <row r="39" spans="1:7">
       <c r="A39" s="16" t="s">
         <v>40</v>
       </c>
@@ -2447,7 +2449,7 @@
       <c r="F39" s="16"/>
       <c r="G39" s="16"/>
     </row>
-    <row r="40" spans="1:7" s="10" customFormat="1">
+    <row r="40" spans="1:7">
       <c r="A40" s="16"/>
       <c r="B40" s="5"/>
       <c r="C40" s="8"/>
@@ -2456,7 +2458,7 @@
       <c r="F40" s="16"/>
       <c r="G40" s="16"/>
     </row>
-    <row r="41" spans="1:7" s="10" customFormat="1">
+    <row r="41" spans="1:7">
       <c r="A41" s="16" t="s">
         <v>41</v>
       </c>
@@ -2473,7 +2475,7 @@
       <c r="F41" s="16"/>
       <c r="G41" s="16"/>
     </row>
-    <row r="42" spans="1:7" s="10" customFormat="1">
+    <row r="42" spans="1:7">
       <c r="A42" s="16" t="s">
         <v>41</v>
       </c>
@@ -2490,7 +2492,7 @@
       <c r="F42" s="16"/>
       <c r="G42" s="16"/>
     </row>
-    <row r="43" spans="1:7" s="10" customFormat="1">
+    <row r="43" spans="1:7">
       <c r="A43" s="16" t="s">
         <v>41</v>
       </c>
@@ -2507,7 +2509,7 @@
       <c r="F43" s="16"/>
       <c r="G43" s="16"/>
     </row>
-    <row r="44" spans="1:7" s="10" customFormat="1">
+    <row r="44" spans="1:7">
       <c r="A44" s="16" t="s">
         <v>41</v>
       </c>
@@ -2524,7 +2526,7 @@
       <c r="F44" s="16"/>
       <c r="G44" s="16"/>
     </row>
-    <row r="45" spans="1:7" s="10" customFormat="1">
+    <row r="45" spans="1:7">
       <c r="A45" s="16" t="s">
         <v>41</v>
       </c>
@@ -2541,7 +2543,7 @@
       <c r="F45" s="16"/>
       <c r="G45" s="16"/>
     </row>
-    <row r="46" spans="1:7" s="10" customFormat="1">
+    <row r="46" spans="1:7">
       <c r="A46" s="16" t="s">
         <v>41</v>
       </c>
@@ -2558,7 +2560,7 @@
       <c r="F46" s="16"/>
       <c r="G46" s="16"/>
     </row>
-    <row r="47" spans="1:7" s="10" customFormat="1">
+    <row r="47" spans="1:7">
       <c r="A47" s="16" t="s">
         <v>41</v>
       </c>
@@ -2575,7 +2577,7 @@
       <c r="F47" s="16"/>
       <c r="G47" s="16"/>
     </row>
-    <row r="48" spans="1:7" s="10" customFormat="1">
+    <row r="48" spans="1:7">
       <c r="A48" s="16" t="s">
         <v>41</v>
       </c>
@@ -2592,7 +2594,7 @@
       <c r="F48" s="16"/>
       <c r="G48" s="16"/>
     </row>
-    <row r="49" spans="1:7" s="10" customFormat="1">
+    <row r="49" spans="1:7">
       <c r="A49" s="16" t="s">
         <v>41</v>
       </c>
@@ -2609,7 +2611,7 @@
       <c r="F49" s="16"/>
       <c r="G49" s="16"/>
     </row>
-    <row r="50" spans="1:7" s="10" customFormat="1">
+    <row r="50" spans="1:7">
       <c r="A50" s="16" t="s">
         <v>41</v>
       </c>
@@ -2626,7 +2628,7 @@
       <c r="F50" s="16"/>
       <c r="G50" s="16"/>
     </row>
-    <row r="51" spans="1:7" s="10" customFormat="1">
+    <row r="51" spans="1:7">
       <c r="A51" s="16" t="s">
         <v>41</v>
       </c>
@@ -2643,7 +2645,7 @@
       <c r="F51" s="16"/>
       <c r="G51" s="16"/>
     </row>
-    <row r="52" spans="1:7" s="10" customFormat="1">
+    <row r="52" spans="1:7">
       <c r="A52" s="16" t="s">
         <v>41</v>
       </c>
@@ -2660,7 +2662,7 @@
       <c r="F52" s="16"/>
       <c r="G52" s="16"/>
     </row>
-    <row r="53" spans="1:7" s="10" customFormat="1">
+    <row r="53" spans="1:7">
       <c r="A53" s="16"/>
       <c r="B53" s="5"/>
       <c r="C53" s="8"/>
@@ -2669,7 +2671,7 @@
       <c r="F53" s="16"/>
       <c r="G53" s="16"/>
     </row>
-    <row r="54" spans="1:7" s="10" customFormat="1">
+    <row r="54" spans="1:7">
       <c r="A54" s="16" t="s">
         <v>99</v>
       </c>
@@ -2686,7 +2688,7 @@
       <c r="F54" s="16"/>
       <c r="G54" s="16"/>
     </row>
-    <row r="55" spans="1:7" s="10" customFormat="1">
+    <row r="55" spans="1:7">
       <c r="A55" s="16" t="s">
         <v>99</v>
       </c>
@@ -2703,7 +2705,7 @@
       <c r="F55" s="16"/>
       <c r="G55" s="16"/>
     </row>
-    <row r="56" spans="1:7" s="10" customFormat="1">
+    <row r="56" spans="1:7">
       <c r="A56" s="16" t="s">
         <v>99</v>
       </c>
@@ -2720,7 +2722,7 @@
       <c r="F56" s="16"/>
       <c r="G56" s="16"/>
     </row>
-    <row r="57" spans="1:7" s="10" customFormat="1">
+    <row r="57" spans="1:7">
       <c r="A57" s="16" t="s">
         <v>99</v>
       </c>
@@ -2737,7 +2739,7 @@
       <c r="F57" s="16"/>
       <c r="G57" s="16"/>
     </row>
-    <row r="58" spans="1:7" s="10" customFormat="1">
+    <row r="58" spans="1:7">
       <c r="A58" s="16" t="s">
         <v>99</v>
       </c>
@@ -2754,7 +2756,7 @@
       <c r="F58" s="16"/>
       <c r="G58" s="16"/>
     </row>
-    <row r="59" spans="1:7" s="10" customFormat="1">
+    <row r="59" spans="1:7">
       <c r="A59" s="16" t="s">
         <v>99</v>
       </c>
@@ -2771,7 +2773,7 @@
       <c r="F59" s="16"/>
       <c r="G59" s="16"/>
     </row>
-    <row r="60" spans="1:7" s="10" customFormat="1">
+    <row r="60" spans="1:7">
       <c r="A60" s="16" t="s">
         <v>99</v>
       </c>
@@ -2788,7 +2790,7 @@
       <c r="F60" s="16"/>
       <c r="G60" s="16"/>
     </row>
-    <row r="61" spans="1:7" s="10" customFormat="1">
+    <row r="61" spans="1:7">
       <c r="A61" s="16" t="s">
         <v>99</v>
       </c>
@@ -2805,7 +2807,7 @@
       <c r="F61" s="16"/>
       <c r="G61" s="16"/>
     </row>
-    <row r="62" spans="1:7" s="10" customFormat="1">
+    <row r="62" spans="1:7">
       <c r="A62" s="16" t="s">
         <v>99</v>
       </c>
@@ -2822,7 +2824,7 @@
       <c r="F62" s="16"/>
       <c r="G62" s="16"/>
     </row>
-    <row r="63" spans="1:7" s="10" customFormat="1">
+    <row r="63" spans="1:7">
       <c r="A63" s="16" t="s">
         <v>99</v>
       </c>
@@ -2839,7 +2841,7 @@
       <c r="F63" s="16"/>
       <c r="G63" s="16"/>
     </row>
-    <row r="64" spans="1:7" s="10" customFormat="1">
+    <row r="64" spans="1:7">
       <c r="A64" s="16" t="s">
         <v>99</v>
       </c>
@@ -2856,7 +2858,7 @@
       <c r="F64" s="16"/>
       <c r="G64" s="16"/>
     </row>
-    <row r="65" spans="1:7" s="10" customFormat="1">
+    <row r="65" spans="1:7">
       <c r="A65" s="16" t="s">
         <v>99</v>
       </c>
@@ -2873,7 +2875,7 @@
       <c r="F65" s="16"/>
       <c r="G65" s="16"/>
     </row>
-    <row r="66" spans="1:7" s="10" customFormat="1">
+    <row r="66" spans="1:7">
       <c r="A66" s="16" t="s">
         <v>99</v>
       </c>
@@ -2890,7 +2892,7 @@
       <c r="F66" s="16"/>
       <c r="G66" s="16"/>
     </row>
-    <row r="67" spans="1:7" s="10" customFormat="1">
+    <row r="67" spans="1:7">
       <c r="A67" s="16" t="s">
         <v>99</v>
       </c>
@@ -2907,7 +2909,7 @@
       <c r="F67" s="16"/>
       <c r="G67" s="16"/>
     </row>
-    <row r="68" spans="1:7" s="10" customFormat="1">
+    <row r="68" spans="1:7">
       <c r="A68" s="16" t="s">
         <v>99</v>
       </c>
@@ -2924,7 +2926,7 @@
       <c r="F68" s="16"/>
       <c r="G68" s="16"/>
     </row>
-    <row r="69" spans="1:7" s="10" customFormat="1">
+    <row r="69" spans="1:7">
       <c r="A69" s="16" t="s">
         <v>99</v>
       </c>
@@ -2941,7 +2943,7 @@
       <c r="F69" s="16"/>
       <c r="G69" s="16"/>
     </row>
-    <row r="70" spans="1:7" s="10" customFormat="1">
+    <row r="70" spans="1:7">
       <c r="A70" s="16" t="s">
         <v>99</v>
       </c>
@@ -2958,7 +2960,7 @@
       <c r="F70" s="16"/>
       <c r="G70" s="16"/>
     </row>
-    <row r="71" spans="1:7" s="10" customFormat="1">
+    <row r="71" spans="1:7">
       <c r="A71" s="16" t="s">
         <v>99</v>
       </c>
@@ -2975,7 +2977,7 @@
       <c r="F71" s="16"/>
       <c r="G71" s="16"/>
     </row>
-    <row r="72" spans="1:7" s="10" customFormat="1">
+    <row r="72" spans="1:7">
       <c r="A72" s="16" t="s">
         <v>99</v>
       </c>
@@ -2992,7 +2994,7 @@
       <c r="F72" s="16"/>
       <c r="G72" s="16"/>
     </row>
-    <row r="73" spans="1:7" s="10" customFormat="1">
+    <row r="73" spans="1:7">
       <c r="A73" s="16" t="s">
         <v>99</v>
       </c>
@@ -3009,7 +3011,7 @@
       <c r="F73" s="16"/>
       <c r="G73" s="16"/>
     </row>
-    <row r="74" spans="1:7" s="10" customFormat="1">
+    <row r="74" spans="1:7">
       <c r="A74" s="16" t="s">
         <v>99</v>
       </c>
@@ -3026,7 +3028,7 @@
       <c r="F74" s="16"/>
       <c r="G74" s="16"/>
     </row>
-    <row r="75" spans="1:7" s="10" customFormat="1">
+    <row r="75" spans="1:7">
       <c r="A75" s="16" t="s">
         <v>99</v>
       </c>
@@ -3043,7 +3045,7 @@
       <c r="F75" s="16"/>
       <c r="G75" s="16"/>
     </row>
-    <row r="76" spans="1:7" s="10" customFormat="1">
+    <row r="76" spans="1:7">
       <c r="A76" s="16" t="s">
         <v>99</v>
       </c>
@@ -3060,7 +3062,7 @@
       <c r="F76" s="16"/>
       <c r="G76" s="16"/>
     </row>
-    <row r="77" spans="1:7" s="10" customFormat="1">
+    <row r="77" spans="1:7">
       <c r="A77" s="16" t="s">
         <v>99</v>
       </c>
@@ -3077,7 +3079,7 @@
       <c r="F77" s="16"/>
       <c r="G77" s="16"/>
     </row>
-    <row r="78" spans="1:7" s="10" customFormat="1">
+    <row r="78" spans="1:7">
       <c r="A78" s="16" t="s">
         <v>99</v>
       </c>
@@ -3094,7 +3096,7 @@
       <c r="F78" s="16"/>
       <c r="G78" s="16"/>
     </row>
-    <row r="79" spans="1:7" s="10" customFormat="1">
+    <row r="79" spans="1:7">
       <c r="A79" s="16" t="s">
         <v>99</v>
       </c>
@@ -3111,7 +3113,7 @@
       <c r="F79" s="16"/>
       <c r="G79" s="16"/>
     </row>
-    <row r="80" spans="1:7" s="10" customFormat="1">
+    <row r="80" spans="1:7">
       <c r="A80" s="16" t="s">
         <v>99</v>
       </c>
@@ -3128,7 +3130,7 @@
       <c r="F80" s="16"/>
       <c r="G80" s="16"/>
     </row>
-    <row r="81" spans="1:7" s="10" customFormat="1">
+    <row r="81" spans="1:7">
       <c r="A81" s="16" t="s">
         <v>99</v>
       </c>
@@ -3145,7 +3147,7 @@
       <c r="F81" s="16"/>
       <c r="G81" s="16"/>
     </row>
-    <row r="82" spans="1:7" s="10" customFormat="1">
+    <row r="82" spans="1:7">
       <c r="A82" s="16" t="s">
         <v>99</v>
       </c>
@@ -3162,7 +3164,7 @@
       <c r="F82" s="16"/>
       <c r="G82" s="16"/>
     </row>
-    <row r="83" spans="1:7" s="10" customFormat="1">
+    <row r="83" spans="1:7">
       <c r="A83" s="16" t="s">
         <v>99</v>
       </c>
@@ -3179,7 +3181,7 @@
       <c r="F83" s="16"/>
       <c r="G83" s="16"/>
     </row>
-    <row r="84" spans="1:7" s="10" customFormat="1">
+    <row r="84" spans="1:7">
       <c r="A84" s="16" t="s">
         <v>99</v>
       </c>
@@ -3196,7 +3198,7 @@
       <c r="F84" s="16"/>
       <c r="G84" s="16"/>
     </row>
-    <row r="85" spans="1:7" s="10" customFormat="1">
+    <row r="85" spans="1:7">
       <c r="A85" s="16" t="s">
         <v>99</v>
       </c>
@@ -3213,7 +3215,7 @@
       <c r="F85" s="16"/>
       <c r="G85" s="16"/>
     </row>
-    <row r="86" spans="1:7" s="10" customFormat="1">
+    <row r="86" spans="1:7">
       <c r="A86" s="16"/>
       <c r="B86" s="16"/>
       <c r="C86" s="17"/>
@@ -3222,7 +3224,7 @@
       <c r="F86" s="16"/>
       <c r="G86" s="16"/>
     </row>
-    <row r="87" spans="1:7" s="10" customFormat="1">
+    <row r="87" spans="1:7">
       <c r="A87" s="16" t="s">
         <v>100</v>
       </c>
@@ -3239,7 +3241,7 @@
       </c>
       <c r="G87" s="16"/>
     </row>
-    <row r="88" spans="1:7" s="10" customFormat="1">
+    <row r="88" spans="1:7">
       <c r="A88" s="16" t="s">
         <v>100</v>
       </c>
@@ -3256,7 +3258,7 @@
       </c>
       <c r="G88" s="16"/>
     </row>
-    <row r="89" spans="1:7" s="10" customFormat="1">
+    <row r="89" spans="1:7">
       <c r="A89" s="16" t="s">
         <v>100</v>
       </c>
@@ -3273,7 +3275,7 @@
       </c>
       <c r="G89" s="16"/>
     </row>
-    <row r="90" spans="1:7" s="10" customFormat="1">
+    <row r="90" spans="1:7">
       <c r="A90" s="16" t="s">
         <v>100</v>
       </c>
@@ -3290,7 +3292,7 @@
       </c>
       <c r="G90" s="16"/>
     </row>
-    <row r="91" spans="1:7" s="10" customFormat="1">
+    <row r="91" spans="1:7">
       <c r="A91" s="16" t="s">
         <v>100</v>
       </c>
@@ -3307,7 +3309,7 @@
       </c>
       <c r="G91" s="16"/>
     </row>
-    <row r="92" spans="1:7" s="10" customFormat="1">
+    <row r="92" spans="1:7">
       <c r="A92" s="16" t="s">
         <v>100</v>
       </c>
@@ -3324,7 +3326,7 @@
       </c>
       <c r="G92" s="16"/>
     </row>
-    <row r="93" spans="1:7" s="10" customFormat="1">
+    <row r="93" spans="1:7">
       <c r="A93" s="16" t="s">
         <v>100</v>
       </c>
@@ -3341,7 +3343,7 @@
       </c>
       <c r="G93" s="16"/>
     </row>
-    <row r="94" spans="1:7" s="10" customFormat="1">
+    <row r="94" spans="1:7">
       <c r="A94" s="16" t="s">
         <v>100</v>
       </c>
@@ -3358,7 +3360,7 @@
       </c>
       <c r="G94" s="16"/>
     </row>
-    <row r="95" spans="1:7" s="10" customFormat="1">
+    <row r="95" spans="1:7">
       <c r="A95" s="16" t="s">
         <v>100</v>
       </c>
@@ -3375,7 +3377,7 @@
       </c>
       <c r="G95" s="16"/>
     </row>
-    <row r="96" spans="1:7" s="10" customFormat="1">
+    <row r="96" spans="1:7">
       <c r="A96" s="16" t="s">
         <v>100</v>
       </c>
@@ -3392,7 +3394,7 @@
       </c>
       <c r="G96" s="16"/>
     </row>
-    <row r="97" spans="1:7" s="10" customFormat="1">
+    <row r="97" spans="1:7">
       <c r="A97" s="16" t="s">
         <v>100</v>
       </c>
@@ -3409,7 +3411,7 @@
       </c>
       <c r="G97" s="16"/>
     </row>
-    <row r="98" spans="1:7" s="10" customFormat="1">
+    <row r="98" spans="1:7">
       <c r="A98" s="16" t="s">
         <v>100</v>
       </c>
@@ -3426,7 +3428,7 @@
       </c>
       <c r="G98" s="16"/>
     </row>
-    <row r="99" spans="1:7" s="10" customFormat="1">
+    <row r="99" spans="1:7">
       <c r="A99" s="16" t="s">
         <v>100</v>
       </c>
@@ -3443,7 +3445,7 @@
       </c>
       <c r="G99" s="16"/>
     </row>
-    <row r="100" spans="1:7" s="10" customFormat="1">
+    <row r="100" spans="1:7">
       <c r="A100" s="16" t="s">
         <v>100</v>
       </c>
@@ -3460,7 +3462,7 @@
       </c>
       <c r="G100" s="16"/>
     </row>
-    <row r="101" spans="1:7" s="10" customFormat="1">
+    <row r="101" spans="1:7">
       <c r="A101" s="16" t="s">
         <v>100</v>
       </c>
@@ -3477,7 +3479,7 @@
       </c>
       <c r="G101" s="16"/>
     </row>
-    <row r="102" spans="1:7" s="10" customFormat="1">
+    <row r="102" spans="1:7">
       <c r="A102" s="16" t="s">
         <v>100</v>
       </c>
@@ -3494,7 +3496,7 @@
       </c>
       <c r="G102" s="16"/>
     </row>
-    <row r="103" spans="1:7" s="10" customFormat="1">
+    <row r="103" spans="1:7">
       <c r="A103" s="16" t="s">
         <v>100</v>
       </c>
@@ -3511,7 +3513,7 @@
       </c>
       <c r="G103" s="16"/>
     </row>
-    <row r="104" spans="1:7" s="10" customFormat="1">
+    <row r="104" spans="1:7">
       <c r="A104" s="16" t="s">
         <v>100</v>
       </c>
@@ -3528,7 +3530,7 @@
       </c>
       <c r="G104" s="16"/>
     </row>
-    <row r="105" spans="1:7" s="10" customFormat="1">
+    <row r="105" spans="1:7">
       <c r="A105" s="16" t="s">
         <v>100</v>
       </c>
@@ -3545,7 +3547,7 @@
       </c>
       <c r="G105" s="16"/>
     </row>
-    <row r="106" spans="1:7" s="10" customFormat="1">
+    <row r="106" spans="1:7">
       <c r="A106" s="16" t="s">
         <v>100</v>
       </c>
@@ -3562,7 +3564,7 @@
       </c>
       <c r="G106" s="16"/>
     </row>
-    <row r="107" spans="1:7" s="10" customFormat="1">
+    <row r="107" spans="1:7">
       <c r="A107" s="16" t="s">
         <v>100</v>
       </c>
@@ -3579,7 +3581,7 @@
       </c>
       <c r="G107" s="16"/>
     </row>
-    <row r="108" spans="1:7" s="10" customFormat="1">
+    <row r="108" spans="1:7">
       <c r="A108" s="16" t="s">
         <v>100</v>
       </c>
@@ -3596,7 +3598,7 @@
       </c>
       <c r="G108" s="16"/>
     </row>
-    <row r="109" spans="1:7" s="10" customFormat="1">
+    <row r="109" spans="1:7">
       <c r="A109" s="16" t="s">
         <v>100</v>
       </c>
@@ -3613,7 +3615,7 @@
       </c>
       <c r="G109" s="16"/>
     </row>
-    <row r="110" spans="1:7" s="10" customFormat="1">
+    <row r="110" spans="1:7">
       <c r="A110" s="16" t="s">
         <v>100</v>
       </c>
@@ -3630,7 +3632,7 @@
       </c>
       <c r="G110" s="16"/>
     </row>
-    <row r="111" spans="1:7" s="10" customFormat="1">
+    <row r="111" spans="1:7">
       <c r="A111" s="16" t="s">
         <v>100</v>
       </c>
@@ -3647,7 +3649,7 @@
       </c>
       <c r="G111" s="16"/>
     </row>
-    <row r="112" spans="1:7" s="10" customFormat="1">
+    <row r="112" spans="1:7">
       <c r="A112" s="16" t="s">
         <v>100</v>
       </c>
@@ -3664,7 +3666,7 @@
       </c>
       <c r="G112" s="16"/>
     </row>
-    <row r="113" spans="1:7" s="10" customFormat="1">
+    <row r="113" spans="1:7">
       <c r="A113" s="16" t="s">
         <v>100</v>
       </c>
@@ -3681,7 +3683,7 @@
       </c>
       <c r="G113" s="16"/>
     </row>
-    <row r="114" spans="1:7" s="10" customFormat="1">
+    <row r="114" spans="1:7">
       <c r="A114" s="16" t="s">
         <v>100</v>
       </c>
@@ -3698,7 +3700,7 @@
       </c>
       <c r="G114" s="16"/>
     </row>
-    <row r="115" spans="1:7" s="10" customFormat="1">
+    <row r="115" spans="1:7">
       <c r="A115" s="16" t="s">
         <v>100</v>
       </c>
@@ -3715,7 +3717,7 @@
       </c>
       <c r="G115" s="16"/>
     </row>
-    <row r="116" spans="1:7" s="10" customFormat="1">
+    <row r="116" spans="1:7">
       <c r="A116" s="16" t="s">
         <v>100</v>
       </c>
@@ -3732,7 +3734,7 @@
       </c>
       <c r="G116" s="16"/>
     </row>
-    <row r="117" spans="1:7" s="10" customFormat="1">
+    <row r="117" spans="1:7">
       <c r="A117" s="16" t="s">
         <v>100</v>
       </c>
@@ -3749,7 +3751,7 @@
       </c>
       <c r="G117" s="16"/>
     </row>
-    <row r="118" spans="1:7" s="10" customFormat="1">
+    <row r="118" spans="1:7">
       <c r="A118" s="16" t="s">
         <v>100</v>
       </c>
@@ -3766,7 +3768,7 @@
       </c>
       <c r="G118" s="16"/>
     </row>
-    <row r="119" spans="1:7" s="10" customFormat="1">
+    <row r="119" spans="1:7">
       <c r="A119" s="16" t="s">
         <v>100</v>
       </c>
@@ -3783,7 +3785,7 @@
       </c>
       <c r="G119" s="16"/>
     </row>
-    <row r="120" spans="1:7" s="10" customFormat="1">
+    <row r="120" spans="1:7">
       <c r="A120" s="16" t="s">
         <v>100</v>
       </c>
@@ -3800,7 +3802,7 @@
       </c>
       <c r="G120" s="16"/>
     </row>
-    <row r="121" spans="1:7" s="10" customFormat="1">
+    <row r="121" spans="1:7">
       <c r="A121" s="16" t="s">
         <v>100</v>
       </c>
@@ -3817,7 +3819,7 @@
       </c>
       <c r="G121" s="16"/>
     </row>
-    <row r="122" spans="1:7" s="10" customFormat="1">
+    <row r="122" spans="1:7">
       <c r="A122" s="16" t="s">
         <v>100</v>
       </c>
@@ -3834,7 +3836,7 @@
       </c>
       <c r="G122" s="16"/>
     </row>
-    <row r="123" spans="1:7" s="10" customFormat="1">
+    <row r="123" spans="1:7">
       <c r="A123" s="16" t="s">
         <v>100</v>
       </c>
@@ -3851,7 +3853,7 @@
       </c>
       <c r="G123" s="16"/>
     </row>
-    <row r="124" spans="1:7" s="10" customFormat="1">
+    <row r="124" spans="1:7">
       <c r="A124" s="16" t="s">
         <v>100</v>
       </c>
@@ -3868,7 +3870,7 @@
       </c>
       <c r="G124" s="16"/>
     </row>
-    <row r="125" spans="1:7" s="10" customFormat="1">
+    <row r="125" spans="1:7">
       <c r="A125" s="16" t="s">
         <v>100</v>
       </c>
@@ -3885,7 +3887,7 @@
       </c>
       <c r="G125" s="16"/>
     </row>
-    <row r="126" spans="1:7" s="10" customFormat="1">
+    <row r="126" spans="1:7">
       <c r="A126" s="16" t="s">
         <v>100</v>
       </c>
@@ -3902,7 +3904,7 @@
       </c>
       <c r="G126" s="16"/>
     </row>
-    <row r="127" spans="1:7" s="10" customFormat="1">
+    <row r="127" spans="1:7">
       <c r="A127" s="16" t="s">
         <v>100</v>
       </c>
@@ -3919,7 +3921,7 @@
       </c>
       <c r="G127" s="16"/>
     </row>
-    <row r="128" spans="1:7" s="10" customFormat="1">
+    <row r="128" spans="1:7">
       <c r="A128" s="16" t="s">
         <v>100</v>
       </c>
@@ -3936,7 +3938,7 @@
       </c>
       <c r="G128" s="16"/>
     </row>
-    <row r="129" spans="1:7" s="10" customFormat="1">
+    <row r="129" spans="1:7">
       <c r="A129" s="16" t="s">
         <v>100</v>
       </c>
@@ -3953,7 +3955,7 @@
       </c>
       <c r="G129" s="16"/>
     </row>
-    <row r="130" spans="1:7" s="10" customFormat="1">
+    <row r="130" spans="1:7">
       <c r="A130" s="16" t="s">
         <v>100</v>
       </c>
@@ -3970,7 +3972,7 @@
       </c>
       <c r="G130" s="16"/>
     </row>
-    <row r="131" spans="1:7" s="10" customFormat="1">
+    <row r="131" spans="1:7">
       <c r="A131" s="16" t="s">
         <v>100</v>
       </c>
@@ -3987,7 +3989,7 @@
       </c>
       <c r="G131" s="16"/>
     </row>
-    <row r="132" spans="1:7" s="10" customFormat="1">
+    <row r="132" spans="1:7">
       <c r="A132" s="16" t="s">
         <v>100</v>
       </c>
@@ -4004,7 +4006,7 @@
       </c>
       <c r="G132" s="16"/>
     </row>
-    <row r="133" spans="1:7" s="10" customFormat="1">
+    <row r="133" spans="1:7">
       <c r="A133" s="16" t="s">
         <v>100</v>
       </c>
@@ -4021,7 +4023,7 @@
       </c>
       <c r="G133" s="16"/>
     </row>
-    <row r="134" spans="1:7" s="10" customFormat="1">
+    <row r="134" spans="1:7">
       <c r="A134" s="16" t="s">
         <v>100</v>
       </c>
@@ -4038,7 +4040,7 @@
       </c>
       <c r="G134" s="16"/>
     </row>
-    <row r="135" spans="1:7" s="10" customFormat="1">
+    <row r="135" spans="1:7">
       <c r="A135" s="16" t="s">
         <v>100</v>
       </c>
@@ -4055,7 +4057,7 @@
       </c>
       <c r="G135" s="16"/>
     </row>
-    <row r="136" spans="1:7" s="10" customFormat="1">
+    <row r="136" spans="1:7">
       <c r="A136" s="16" t="s">
         <v>100</v>
       </c>
@@ -4072,7 +4074,7 @@
       </c>
       <c r="G136" s="16"/>
     </row>
-    <row r="137" spans="1:7" s="10" customFormat="1">
+    <row r="137" spans="1:7">
       <c r="A137" s="16" t="s">
         <v>100</v>
       </c>
@@ -4089,7 +4091,7 @@
       </c>
       <c r="G137" s="16"/>
     </row>
-    <row r="138" spans="1:7" s="10" customFormat="1">
+    <row r="138" spans="1:7">
       <c r="A138" s="16" t="s">
         <v>100</v>
       </c>
@@ -4106,7 +4108,7 @@
       </c>
       <c r="G138" s="16"/>
     </row>
-    <row r="139" spans="1:7" s="10" customFormat="1">
+    <row r="139" spans="1:7">
       <c r="A139" s="16" t="s">
         <v>100</v>
       </c>
@@ -4123,7 +4125,7 @@
       </c>
       <c r="G139" s="16"/>
     </row>
-    <row r="140" spans="1:7" s="10" customFormat="1">
+    <row r="140" spans="1:7">
       <c r="A140" s="16" t="s">
         <v>100</v>
       </c>
@@ -4140,7 +4142,7 @@
       </c>
       <c r="G140" s="16"/>
     </row>
-    <row r="141" spans="1:7" s="10" customFormat="1">
+    <row r="141" spans="1:7">
       <c r="A141" s="16" t="s">
         <v>100</v>
       </c>
@@ -4157,7 +4159,7 @@
       </c>
       <c r="G141" s="16"/>
     </row>
-    <row r="142" spans="1:7" s="10" customFormat="1">
+    <row r="142" spans="1:7">
       <c r="A142" s="16" t="s">
         <v>100</v>
       </c>
@@ -4174,7 +4176,7 @@
       </c>
       <c r="G142" s="16"/>
     </row>
-    <row r="143" spans="1:7" s="10" customFormat="1">
+    <row r="143" spans="1:7">
       <c r="A143" s="16" t="s">
         <v>100</v>
       </c>
@@ -4191,7 +4193,7 @@
       </c>
       <c r="G143" s="16"/>
     </row>
-    <row r="144" spans="1:7" s="10" customFormat="1">
+    <row r="144" spans="1:7">
       <c r="A144" s="16" t="s">
         <v>100</v>
       </c>
@@ -4208,7 +4210,7 @@
       </c>
       <c r="G144" s="16"/>
     </row>
-    <row r="145" spans="1:7" s="10" customFormat="1">
+    <row r="145" spans="1:7">
       <c r="A145" s="16" t="s">
         <v>100</v>
       </c>
@@ -4225,7 +4227,7 @@
       </c>
       <c r="G145" s="16"/>
     </row>
-    <row r="146" spans="1:7" s="10" customFormat="1">
+    <row r="146" spans="1:7">
       <c r="A146" s="16" t="s">
         <v>100</v>
       </c>
@@ -4242,7 +4244,7 @@
       </c>
       <c r="G146" s="16"/>
     </row>
-    <row r="147" spans="1:7" s="10" customFormat="1">
+    <row r="147" spans="1:7">
       <c r="A147" s="16" t="s">
         <v>100</v>
       </c>
@@ -4259,7 +4261,7 @@
       </c>
       <c r="G147" s="16"/>
     </row>
-    <row r="148" spans="1:7" s="10" customFormat="1">
+    <row r="148" spans="1:7">
       <c r="A148" s="16" t="s">
         <v>100</v>
       </c>
@@ -4276,7 +4278,7 @@
       </c>
       <c r="G148" s="16"/>
     </row>
-    <row r="149" spans="1:7" s="10" customFormat="1">
+    <row r="149" spans="1:7">
       <c r="A149" s="16" t="s">
         <v>100</v>
       </c>
@@ -4293,7 +4295,7 @@
       </c>
       <c r="G149" s="16"/>
     </row>
-    <row r="150" spans="1:7" s="10" customFormat="1">
+    <row r="150" spans="1:7">
       <c r="A150" s="16" t="s">
         <v>100</v>
       </c>
@@ -4310,7 +4312,7 @@
       </c>
       <c r="G150" s="16"/>
     </row>
-    <row r="151" spans="1:7" s="10" customFormat="1">
+    <row r="151" spans="1:7">
       <c r="A151" s="16" t="s">
         <v>100</v>
       </c>
@@ -4327,7 +4329,7 @@
       </c>
       <c r="G151" s="16"/>
     </row>
-    <row r="152" spans="1:7" s="10" customFormat="1">
+    <row r="152" spans="1:7">
       <c r="A152" s="16" t="s">
         <v>100</v>
       </c>
@@ -4344,7 +4346,7 @@
       </c>
       <c r="G152" s="16"/>
     </row>
-    <row r="153" spans="1:7" s="10" customFormat="1">
+    <row r="153" spans="1:7">
       <c r="A153" s="16" t="s">
         <v>100</v>
       </c>
@@ -4361,7 +4363,7 @@
       </c>
       <c r="G153" s="16"/>
     </row>
-    <row r="154" spans="1:7" s="10" customFormat="1">
+    <row r="154" spans="1:7">
       <c r="A154" s="16" t="s">
         <v>100</v>
       </c>
@@ -4378,7 +4380,7 @@
       </c>
       <c r="G154" s="16"/>
     </row>
-    <row r="155" spans="1:7" s="10" customFormat="1">
+    <row r="155" spans="1:7">
       <c r="A155" s="16" t="s">
         <v>100</v>
       </c>
@@ -4395,7 +4397,7 @@
       </c>
       <c r="G155" s="16"/>
     </row>
-    <row r="156" spans="1:7" s="10" customFormat="1">
+    <row r="156" spans="1:7">
       <c r="A156" s="16" t="s">
         <v>100</v>
       </c>
@@ -4412,7 +4414,7 @@
       </c>
       <c r="G156" s="16"/>
     </row>
-    <row r="157" spans="1:7" s="10" customFormat="1">
+    <row r="157" spans="1:7">
       <c r="A157" s="16" t="s">
         <v>100</v>
       </c>
@@ -4429,7 +4431,7 @@
       </c>
       <c r="G157" s="16"/>
     </row>
-    <row r="158" spans="1:7" s="10" customFormat="1">
+    <row r="158" spans="1:7">
       <c r="A158" s="16" t="s">
         <v>100</v>
       </c>
@@ -4446,7 +4448,7 @@
       </c>
       <c r="G158" s="16"/>
     </row>
-    <row r="159" spans="1:7" s="10" customFormat="1">
+    <row r="159" spans="1:7">
       <c r="A159" s="16" t="s">
         <v>100</v>
       </c>
@@ -4463,7 +4465,7 @@
       </c>
       <c r="G159" s="16"/>
     </row>
-    <row r="160" spans="1:7" s="10" customFormat="1">
+    <row r="160" spans="1:7">
       <c r="A160" s="16" t="s">
         <v>100</v>
       </c>
@@ -4480,7 +4482,7 @@
       </c>
       <c r="G160" s="16"/>
     </row>
-    <row r="161" spans="1:7" s="10" customFormat="1">
+    <row r="161" spans="1:7">
       <c r="A161" s="16" t="s">
         <v>100</v>
       </c>
@@ -4497,7 +4499,7 @@
       </c>
       <c r="G161" s="16"/>
     </row>
-    <row r="162" spans="1:7" s="10" customFormat="1">
+    <row r="162" spans="1:7">
       <c r="A162" s="16" t="s">
         <v>100</v>
       </c>
@@ -4514,7 +4516,7 @@
       </c>
       <c r="G162" s="16"/>
     </row>
-    <row r="163" spans="1:7" s="10" customFormat="1">
+    <row r="163" spans="1:7">
       <c r="A163" s="16" t="s">
         <v>100</v>
       </c>
@@ -4531,7 +4533,7 @@
       </c>
       <c r="G163" s="16"/>
     </row>
-    <row r="164" spans="1:7" s="10" customFormat="1">
+    <row r="164" spans="1:7">
       <c r="A164" s="16" t="s">
         <v>100</v>
       </c>
@@ -4548,7 +4550,7 @@
       </c>
       <c r="G164" s="16"/>
     </row>
-    <row r="165" spans="1:7" s="10" customFormat="1">
+    <row r="165" spans="1:7">
       <c r="A165" s="16" t="s">
         <v>100</v>
       </c>
@@ -4565,7 +4567,7 @@
       </c>
       <c r="G165" s="16"/>
     </row>
-    <row r="166" spans="1:7" s="10" customFormat="1">
+    <row r="166" spans="1:7">
       <c r="A166" s="16" t="s">
         <v>100</v>
       </c>
@@ -4582,7 +4584,7 @@
       </c>
       <c r="G166" s="16"/>
     </row>
-    <row r="167" spans="1:7" s="10" customFormat="1">
+    <row r="167" spans="1:7">
       <c r="A167" s="16" t="s">
         <v>100</v>
       </c>
@@ -4599,7 +4601,7 @@
       </c>
       <c r="G167" s="16"/>
     </row>
-    <row r="168" spans="1:7" s="10" customFormat="1">
+    <row r="168" spans="1:7">
       <c r="A168" s="16" t="s">
         <v>100</v>
       </c>
@@ -4616,7 +4618,7 @@
       </c>
       <c r="G168" s="16"/>
     </row>
-    <row r="169" spans="1:7" s="10" customFormat="1">
+    <row r="169" spans="1:7">
       <c r="A169" s="16" t="s">
         <v>100</v>
       </c>
@@ -4633,7 +4635,7 @@
       </c>
       <c r="G169" s="16"/>
     </row>
-    <row r="170" spans="1:7" s="10" customFormat="1">
+    <row r="170" spans="1:7">
       <c r="A170" s="16" t="s">
         <v>100</v>
       </c>
@@ -4650,7 +4652,7 @@
       </c>
       <c r="G170" s="16"/>
     </row>
-    <row r="171" spans="1:7" s="10" customFormat="1">
+    <row r="171" spans="1:7">
       <c r="A171" s="16" t="s">
         <v>100</v>
       </c>
@@ -4667,7 +4669,7 @@
       </c>
       <c r="G171" s="16"/>
     </row>
-    <row r="172" spans="1:7" s="10" customFormat="1">
+    <row r="172" spans="1:7">
       <c r="A172" s="16" t="s">
         <v>100</v>
       </c>
@@ -4684,7 +4686,7 @@
       </c>
       <c r="G172" s="16"/>
     </row>
-    <row r="173" spans="1:7" s="10" customFormat="1">
+    <row r="173" spans="1:7">
       <c r="A173" s="16" t="s">
         <v>100</v>
       </c>
@@ -4701,7 +4703,7 @@
       </c>
       <c r="G173" s="16"/>
     </row>
-    <row r="174" spans="1:7" s="10" customFormat="1">
+    <row r="174" spans="1:7">
       <c r="A174" s="16" t="s">
         <v>100</v>
       </c>
@@ -4718,7 +4720,7 @@
       </c>
       <c r="G174" s="16"/>
     </row>
-    <row r="175" spans="1:7" s="10" customFormat="1">
+    <row r="175" spans="1:7">
       <c r="A175" s="16" t="s">
         <v>100</v>
       </c>
@@ -4735,7 +4737,7 @@
       </c>
       <c r="G175" s="16"/>
     </row>
-    <row r="176" spans="1:7" s="10" customFormat="1">
+    <row r="176" spans="1:7">
       <c r="A176" s="16" t="s">
         <v>100</v>
       </c>
@@ -4752,7 +4754,7 @@
       </c>
       <c r="G176" s="16"/>
     </row>
-    <row r="177" spans="1:7" s="10" customFormat="1">
+    <row r="177" spans="1:7">
       <c r="A177" s="16" t="s">
         <v>100</v>
       </c>
@@ -4769,7 +4771,7 @@
       </c>
       <c r="G177" s="16"/>
     </row>
-    <row r="178" spans="1:7" s="10" customFormat="1">
+    <row r="178" spans="1:7">
       <c r="A178" s="16" t="s">
         <v>100</v>
       </c>
@@ -4786,7 +4788,7 @@
       </c>
       <c r="G178" s="16"/>
     </row>
-    <row r="179" spans="1:7" s="10" customFormat="1">
+    <row r="179" spans="1:7">
       <c r="A179" s="16" t="s">
         <v>100</v>
       </c>
@@ -4803,7 +4805,7 @@
       </c>
       <c r="G179" s="16"/>
     </row>
-    <row r="180" spans="1:7" s="10" customFormat="1">
+    <row r="180" spans="1:7">
       <c r="A180" s="16" t="s">
         <v>100</v>
       </c>
@@ -4820,7 +4822,7 @@
       </c>
       <c r="G180" s="16"/>
     </row>
-    <row r="181" spans="1:7" s="10" customFormat="1">
+    <row r="181" spans="1:7">
       <c r="A181" s="16" t="s">
         <v>100</v>
       </c>
@@ -4837,7 +4839,7 @@
       </c>
       <c r="G181" s="16"/>
     </row>
-    <row r="182" spans="1:7" s="10" customFormat="1">
+    <row r="182" spans="1:7">
       <c r="A182" s="16" t="s">
         <v>100</v>
       </c>
@@ -4854,7 +4856,7 @@
       </c>
       <c r="G182" s="16"/>
     </row>
-    <row r="183" spans="1:7" s="10" customFormat="1">
+    <row r="183" spans="1:7">
       <c r="A183" s="16" t="s">
         <v>100</v>
       </c>
@@ -4871,7 +4873,7 @@
       </c>
       <c r="G183" s="16"/>
     </row>
-    <row r="184" spans="1:7" s="10" customFormat="1">
+    <row r="184" spans="1:7">
       <c r="A184" s="16" t="s">
         <v>100</v>
       </c>
@@ -4888,7 +4890,7 @@
       </c>
       <c r="G184" s="16"/>
     </row>
-    <row r="185" spans="1:7" s="10" customFormat="1">
+    <row r="185" spans="1:7">
       <c r="A185" s="16" t="s">
         <v>100</v>
       </c>
@@ -4905,7 +4907,7 @@
       </c>
       <c r="G185" s="16"/>
     </row>
-    <row r="186" spans="1:7" s="10" customFormat="1">
+    <row r="186" spans="1:7">
       <c r="A186" s="16" t="s">
         <v>100</v>
       </c>
@@ -4922,7 +4924,7 @@
       </c>
       <c r="G186" s="16"/>
     </row>
-    <row r="187" spans="1:7" s="10" customFormat="1">
+    <row r="187" spans="1:7">
       <c r="A187" s="16" t="s">
         <v>100</v>
       </c>
@@ -4939,7 +4941,7 @@
       </c>
       <c r="G187" s="16"/>
     </row>
-    <row r="188" spans="1:7" s="10" customFormat="1">
+    <row r="188" spans="1:7">
       <c r="A188" s="16" t="s">
         <v>100</v>
       </c>
@@ -4956,7 +4958,7 @@
       </c>
       <c r="G188" s="16"/>
     </row>
-    <row r="189" spans="1:7" s="10" customFormat="1">
+    <row r="189" spans="1:7">
       <c r="A189" s="16" t="s">
         <v>100</v>
       </c>
@@ -4973,7 +4975,7 @@
       </c>
       <c r="G189" s="16"/>
     </row>
-    <row r="190" spans="1:7" s="10" customFormat="1">
+    <row r="190" spans="1:7">
       <c r="A190" s="16" t="s">
         <v>100</v>
       </c>
@@ -4990,7 +4992,7 @@
       </c>
       <c r="G190" s="16"/>
     </row>
-    <row r="191" spans="1:7" s="10" customFormat="1">
+    <row r="191" spans="1:7">
       <c r="A191" s="16" t="s">
         <v>100</v>
       </c>
@@ -5007,7 +5009,7 @@
       </c>
       <c r="G191" s="16"/>
     </row>
-    <row r="192" spans="1:7" s="10" customFormat="1">
+    <row r="192" spans="1:7">
       <c r="A192" s="16" t="s">
         <v>100</v>
       </c>
@@ -5024,7 +5026,7 @@
       </c>
       <c r="G192" s="16"/>
     </row>
-    <row r="193" spans="1:7" s="10" customFormat="1">
+    <row r="193" spans="1:7">
       <c r="A193" s="16" t="s">
         <v>100</v>
       </c>
@@ -5041,7 +5043,7 @@
       </c>
       <c r="G193" s="16"/>
     </row>
-    <row r="194" spans="1:7" s="10" customFormat="1">
+    <row r="194" spans="1:7">
       <c r="A194" s="16" t="s">
         <v>100</v>
       </c>
@@ -5058,7 +5060,7 @@
       </c>
       <c r="G194" s="16"/>
     </row>
-    <row r="195" spans="1:7" s="10" customFormat="1">
+    <row r="195" spans="1:7">
       <c r="A195" s="16" t="s">
         <v>100</v>
       </c>
@@ -5075,7 +5077,7 @@
       </c>
       <c r="G195" s="16"/>
     </row>
-    <row r="196" spans="1:7" s="10" customFormat="1">
+    <row r="196" spans="1:7">
       <c r="A196" s="16" t="s">
         <v>100</v>
       </c>
@@ -5092,7 +5094,7 @@
       </c>
       <c r="G196" s="16"/>
     </row>
-    <row r="197" spans="1:7" s="10" customFormat="1">
+    <row r="197" spans="1:7">
       <c r="A197" s="16" t="s">
         <v>100</v>
       </c>
@@ -5109,7 +5111,7 @@
       </c>
       <c r="G197" s="16"/>
     </row>
-    <row r="198" spans="1:7" s="10" customFormat="1">
+    <row r="198" spans="1:7">
       <c r="A198" s="16" t="s">
         <v>100</v>
       </c>
@@ -5126,7 +5128,7 @@
       </c>
       <c r="G198" s="16"/>
     </row>
-    <row r="199" spans="1:7" s="10" customFormat="1">
+    <row r="199" spans="1:7">
       <c r="A199" s="16" t="s">
         <v>100</v>
       </c>
@@ -5143,7 +5145,7 @@
       </c>
       <c r="G199" s="16"/>
     </row>
-    <row r="200" spans="1:7" s="10" customFormat="1">
+    <row r="200" spans="1:7">
       <c r="A200" s="16" t="s">
         <v>100</v>
       </c>
@@ -5160,7 +5162,7 @@
       </c>
       <c r="G200" s="16"/>
     </row>
-    <row r="201" spans="1:7" s="10" customFormat="1">
+    <row r="201" spans="1:7">
       <c r="A201" s="16" t="s">
         <v>100</v>
       </c>
@@ -5177,7 +5179,7 @@
       </c>
       <c r="G201" s="16"/>
     </row>
-    <row r="202" spans="1:7" s="10" customFormat="1">
+    <row r="202" spans="1:7">
       <c r="A202" s="16" t="s">
         <v>100</v>
       </c>
@@ -5194,7 +5196,7 @@
       </c>
       <c r="G202" s="16"/>
     </row>
-    <row r="203" spans="1:7" s="10" customFormat="1">
+    <row r="203" spans="1:7">
       <c r="A203" s="16" t="s">
         <v>100</v>
       </c>
@@ -5211,7 +5213,7 @@
       </c>
       <c r="G203" s="16"/>
     </row>
-    <row r="204" spans="1:7" s="10" customFormat="1">
+    <row r="204" spans="1:7">
       <c r="A204" s="16" t="s">
         <v>100</v>
       </c>
@@ -5228,7 +5230,7 @@
       </c>
       <c r="G204" s="16"/>
     </row>
-    <row r="205" spans="1:7" s="10" customFormat="1">
+    <row r="205" spans="1:7">
       <c r="A205" s="16" t="s">
         <v>100</v>
       </c>
@@ -5245,7 +5247,7 @@
       </c>
       <c r="G205" s="16"/>
     </row>
-    <row r="206" spans="1:7" s="10" customFormat="1">
+    <row r="206" spans="1:7">
       <c r="A206" s="16" t="s">
         <v>100</v>
       </c>
@@ -5262,7 +5264,7 @@
       </c>
       <c r="G206" s="16"/>
     </row>
-    <row r="207" spans="1:7" s="10" customFormat="1">
+    <row r="207" spans="1:7">
       <c r="A207" s="16" t="s">
         <v>100</v>
       </c>
@@ -5279,7 +5281,7 @@
       </c>
       <c r="G207" s="16"/>
     </row>
-    <row r="208" spans="1:7" s="10" customFormat="1">
+    <row r="208" spans="1:7">
       <c r="A208" s="16" t="s">
         <v>100</v>
       </c>
@@ -5296,7 +5298,7 @@
       </c>
       <c r="G208" s="16"/>
     </row>
-    <row r="209" spans="1:7" s="10" customFormat="1">
+    <row r="209" spans="1:7">
       <c r="A209" s="16" t="s">
         <v>100</v>
       </c>
@@ -5313,7 +5315,7 @@
       </c>
       <c r="G209" s="16"/>
     </row>
-    <row r="210" spans="1:7" s="10" customFormat="1">
+    <row r="210" spans="1:7">
       <c r="A210" s="16" t="s">
         <v>100</v>
       </c>
@@ -5330,7 +5332,7 @@
       </c>
       <c r="G210" s="16"/>
     </row>
-    <row r="211" spans="1:7" s="10" customFormat="1">
+    <row r="211" spans="1:7">
       <c r="A211" s="16" t="s">
         <v>100</v>
       </c>
@@ -5347,7 +5349,7 @@
       </c>
       <c r="G211" s="16"/>
     </row>
-    <row r="212" spans="1:7" s="10" customFormat="1">
+    <row r="212" spans="1:7">
       <c r="A212" s="16" t="s">
         <v>100</v>
       </c>
@@ -5364,7 +5366,7 @@
       </c>
       <c r="G212" s="16"/>
     </row>
-    <row r="213" spans="1:7" s="10" customFormat="1">
+    <row r="213" spans="1:7">
       <c r="A213" s="16" t="s">
         <v>100</v>
       </c>
@@ -5381,7 +5383,7 @@
       </c>
       <c r="G213" s="16"/>
     </row>
-    <row r="214" spans="1:7" s="10" customFormat="1">
+    <row r="214" spans="1:7">
       <c r="A214" s="16" t="s">
         <v>100</v>
       </c>
@@ -5398,7 +5400,7 @@
       </c>
       <c r="G214" s="16"/>
     </row>
-    <row r="215" spans="1:7" s="10" customFormat="1">
+    <row r="215" spans="1:7">
       <c r="A215" s="16" t="s">
         <v>100</v>
       </c>
@@ -5415,7 +5417,7 @@
       </c>
       <c r="G215" s="16"/>
     </row>
-    <row r="216" spans="1:7" s="10" customFormat="1">
+    <row r="216" spans="1:7">
       <c r="A216" s="16" t="s">
         <v>100</v>
       </c>
@@ -5432,7 +5434,7 @@
       </c>
       <c r="G216" s="16"/>
     </row>
-    <row r="217" spans="1:7" s="10" customFormat="1">
+    <row r="217" spans="1:7">
       <c r="A217" s="16" t="s">
         <v>100</v>
       </c>
@@ -5449,7 +5451,7 @@
       </c>
       <c r="G217" s="16"/>
     </row>
-    <row r="218" spans="1:7" s="10" customFormat="1">
+    <row r="218" spans="1:7">
       <c r="A218" s="16" t="s">
         <v>100</v>
       </c>
@@ -5466,7 +5468,7 @@
       </c>
       <c r="G218" s="16"/>
     </row>
-    <row r="219" spans="1:7" s="10" customFormat="1">
+    <row r="219" spans="1:7">
       <c r="A219" s="16"/>
       <c r="B219" s="16"/>
       <c r="C219" s="17"/>
@@ -5475,7 +5477,7 @@
       <c r="F219" s="16"/>
       <c r="G219" s="16"/>
     </row>
-    <row r="220" spans="1:7" s="10" customFormat="1">
+    <row r="220" spans="1:7">
       <c r="A220" s="16" t="s">
         <v>213</v>
       </c>
@@ -5492,7 +5494,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="221" spans="1:7" s="10" customFormat="1">
+    <row r="221" spans="1:7">
       <c r="A221" s="16" t="s">
         <v>213</v>
       </c>
@@ -5509,7 +5511,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="222" spans="1:7" s="10" customFormat="1">
+    <row r="222" spans="1:7">
       <c r="A222" s="16" t="s">
         <v>213</v>
       </c>
@@ -5526,7 +5528,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="223" spans="1:7" s="10" customFormat="1">
+    <row r="223" spans="1:7">
       <c r="A223" s="16" t="s">
         <v>213</v>
       </c>
@@ -5543,7 +5545,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="224" spans="1:7" s="10" customFormat="1">
+    <row r="224" spans="1:7">
       <c r="A224" s="16" t="s">
         <v>213</v>
       </c>
@@ -5560,7 +5562,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="225" spans="1:7" s="10" customFormat="1">
+    <row r="225" spans="1:7">
       <c r="A225" s="16" t="s">
         <v>213</v>
       </c>
@@ -5577,7 +5579,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="226" spans="1:7" s="10" customFormat="1">
+    <row r="226" spans="1:7">
       <c r="A226" s="16" t="s">
         <v>213</v>
       </c>
@@ -5594,7 +5596,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="227" spans="1:7" s="10" customFormat="1">
+    <row r="227" spans="1:7">
       <c r="A227" s="16" t="s">
         <v>213</v>
       </c>
@@ -5611,7 +5613,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="228" spans="1:7" s="10" customFormat="1">
+    <row r="228" spans="1:7">
       <c r="A228" s="16" t="s">
         <v>213</v>
       </c>
@@ -5628,7 +5630,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="229" spans="1:7" s="10" customFormat="1">
+    <row r="229" spans="1:7">
       <c r="A229" s="16" t="s">
         <v>213</v>
       </c>
@@ -5645,7 +5647,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="230" spans="1:7" s="10" customFormat="1">
+    <row r="230" spans="1:7">
       <c r="A230" s="16" t="s">
         <v>213</v>
       </c>
@@ -5662,7 +5664,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="231" spans="1:7" s="10" customFormat="1">
+    <row r="231" spans="1:7">
       <c r="A231" s="16" t="s">
         <v>213</v>
       </c>
@@ -5679,7 +5681,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="232" spans="1:7" s="10" customFormat="1">
+    <row r="232" spans="1:7">
       <c r="A232" s="16" t="s">
         <v>213</v>
       </c>
@@ -5696,7 +5698,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="233" spans="1:7" s="10" customFormat="1">
+    <row r="233" spans="1:7">
       <c r="A233" s="16" t="s">
         <v>213</v>
       </c>
@@ -5713,7 +5715,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="234" spans="1:7" s="10" customFormat="1">
+    <row r="234" spans="1:7">
       <c r="A234" s="16" t="s">
         <v>213</v>
       </c>
@@ -5730,7 +5732,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="235" spans="1:7" s="10" customFormat="1">
+    <row r="235" spans="1:7">
       <c r="A235" s="16" t="s">
         <v>213</v>
       </c>
@@ -5747,7 +5749,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="236" spans="1:7" s="10" customFormat="1">
+    <row r="236" spans="1:7">
       <c r="A236" s="16" t="s">
         <v>213</v>
       </c>
@@ -5764,7 +5766,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="237" spans="1:7" s="10" customFormat="1">
+    <row r="237" spans="1:7">
       <c r="A237" s="16" t="s">
         <v>213</v>
       </c>
@@ -5781,7 +5783,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="238" spans="1:7" s="10" customFormat="1">
+    <row r="238" spans="1:7">
       <c r="A238" s="16" t="s">
         <v>213</v>
       </c>
@@ -5798,7 +5800,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="239" spans="1:7" s="10" customFormat="1">
+    <row r="239" spans="1:7">
       <c r="A239" s="16" t="s">
         <v>213</v>
       </c>
@@ -5815,7 +5817,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="240" spans="1:7" s="10" customFormat="1">
+    <row r="240" spans="1:7">
       <c r="A240" s="16" t="s">
         <v>213</v>
       </c>
@@ -5832,7 +5834,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="241" spans="1:7" s="10" customFormat="1">
+    <row r="241" spans="1:7">
       <c r="A241" s="16" t="s">
         <v>213</v>
       </c>
@@ -5849,7 +5851,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="242" spans="1:7" s="10" customFormat="1">
+    <row r="242" spans="1:7">
       <c r="A242" s="16" t="s">
         <v>213</v>
       </c>
@@ -5866,7 +5868,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="243" spans="1:7" s="10" customFormat="1">
+    <row r="243" spans="1:7">
       <c r="A243" s="16" t="s">
         <v>213</v>
       </c>
@@ -5883,7 +5885,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="244" spans="1:7" s="10" customFormat="1">
+    <row r="244" spans="1:7">
       <c r="A244" s="16" t="s">
         <v>213</v>
       </c>
@@ -5900,7 +5902,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="245" spans="1:7" s="10" customFormat="1">
+    <row r="245" spans="1:7">
       <c r="A245" s="16" t="s">
         <v>213</v>
       </c>
@@ -5917,7 +5919,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="246" spans="1:7" s="10" customFormat="1">
+    <row r="246" spans="1:7">
       <c r="A246" s="16" t="s">
         <v>213</v>
       </c>
@@ -5934,7 +5936,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="247" spans="1:7" s="10" customFormat="1">
+    <row r="247" spans="1:7">
       <c r="A247" s="16" t="s">
         <v>213</v>
       </c>
@@ -5951,7 +5953,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="248" spans="1:7" s="10" customFormat="1">
+    <row r="248" spans="1:7">
       <c r="A248" s="16" t="s">
         <v>213</v>
       </c>
@@ -5968,7 +5970,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="249" spans="1:7" s="10" customFormat="1">
+    <row r="249" spans="1:7">
       <c r="A249" s="16" t="s">
         <v>213</v>
       </c>
@@ -5985,7 +5987,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="250" spans="1:7" s="10" customFormat="1">
+    <row r="250" spans="1:7">
       <c r="A250" s="16" t="s">
         <v>213</v>
       </c>
@@ -6002,7 +6004,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="251" spans="1:7" s="10" customFormat="1">
+    <row r="251" spans="1:7">
       <c r="A251" s="16" t="s">
         <v>213</v>
       </c>
@@ -6019,7 +6021,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="252" spans="1:7" s="10" customFormat="1">
+    <row r="252" spans="1:7">
       <c r="A252" s="16" t="s">
         <v>213</v>
       </c>
@@ -6036,7 +6038,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="253" spans="1:7" s="10" customFormat="1">
+    <row r="253" spans="1:7">
       <c r="A253" s="16" t="s">
         <v>213</v>
       </c>
@@ -6053,7 +6055,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="254" spans="1:7" s="10" customFormat="1">
+    <row r="254" spans="1:7">
       <c r="A254" s="16" t="s">
         <v>213</v>
       </c>
@@ -6070,7 +6072,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="255" spans="1:7" s="10" customFormat="1">
+    <row r="255" spans="1:7">
       <c r="A255" s="16" t="s">
         <v>213</v>
       </c>
@@ -6087,7 +6089,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="256" spans="1:7" s="10" customFormat="1">
+    <row r="256" spans="1:7">
       <c r="A256" s="16" t="s">
         <v>213</v>
       </c>
@@ -6104,7 +6106,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="257" spans="1:7" s="10" customFormat="1">
+    <row r="257" spans="1:7">
       <c r="A257" s="16" t="s">
         <v>213</v>
       </c>
@@ -6121,7 +6123,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="258" spans="1:7" s="10" customFormat="1">
+    <row r="258" spans="1:7">
       <c r="A258" s="16" t="s">
         <v>213</v>
       </c>
@@ -6138,7 +6140,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="259" spans="1:7" s="10" customFormat="1">
+    <row r="259" spans="1:7">
       <c r="A259" s="16" t="s">
         <v>213</v>
       </c>
@@ -6155,7 +6157,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="260" spans="1:7" s="10" customFormat="1">
+    <row r="260" spans="1:7">
       <c r="A260" s="16" t="s">
         <v>213</v>
       </c>
@@ -6172,7 +6174,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="261" spans="1:7" s="10" customFormat="1">
+    <row r="261" spans="1:7">
       <c r="A261" s="16" t="s">
         <v>213</v>
       </c>
@@ -6189,7 +6191,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="262" spans="1:7" s="10" customFormat="1">
+    <row r="262" spans="1:7">
       <c r="A262" s="16" t="s">
         <v>213</v>
       </c>
@@ -6206,7 +6208,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="263" spans="1:7" s="10" customFormat="1">
+    <row r="263" spans="1:7">
       <c r="A263" s="16" t="s">
         <v>213</v>
       </c>
@@ -6223,7 +6225,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="264" spans="1:7" s="10" customFormat="1">
+    <row r="264" spans="1:7">
       <c r="A264" s="16" t="s">
         <v>213</v>
       </c>
@@ -6240,7 +6242,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="265" spans="1:7" s="10" customFormat="1">
+    <row r="265" spans="1:7">
       <c r="A265" s="16" t="s">
         <v>213</v>
       </c>
@@ -6257,7 +6259,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="266" spans="1:7" s="10" customFormat="1">
+    <row r="266" spans="1:7">
       <c r="A266" s="16" t="s">
         <v>213</v>
       </c>
@@ -6274,7 +6276,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="267" spans="1:7" s="10" customFormat="1">
+    <row r="267" spans="1:7">
       <c r="A267" s="16" t="s">
         <v>213</v>
       </c>
@@ -6291,7 +6293,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="268" spans="1:7" s="10" customFormat="1">
+    <row r="268" spans="1:7">
       <c r="A268" s="16" t="s">
         <v>213</v>
       </c>
@@ -6308,7 +6310,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="269" spans="1:7" s="10" customFormat="1">
+    <row r="269" spans="1:7">
       <c r="A269" s="16" t="s">
         <v>213</v>
       </c>
@@ -6325,7 +6327,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="270" spans="1:7" s="10" customFormat="1">
+    <row r="270" spans="1:7">
       <c r="A270" s="16" t="s">
         <v>213</v>
       </c>
@@ -6342,7 +6344,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="271" spans="1:7" s="10" customFormat="1">
+    <row r="271" spans="1:7">
       <c r="A271" s="16" t="s">
         <v>213</v>
       </c>
@@ -6359,7 +6361,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="272" spans="1:7" s="10" customFormat="1">
+    <row r="272" spans="1:7">
       <c r="A272" s="16" t="s">
         <v>213</v>
       </c>
@@ -6376,7 +6378,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="273" spans="1:7" s="10" customFormat="1">
+    <row r="273" spans="1:7">
       <c r="A273" s="16" t="s">
         <v>213</v>
       </c>
@@ -6393,7 +6395,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="274" spans="1:7" s="10" customFormat="1">
+    <row r="274" spans="1:7">
       <c r="A274" s="16" t="s">
         <v>213</v>
       </c>
@@ -6410,7 +6412,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="275" spans="1:7" s="10" customFormat="1">
+    <row r="275" spans="1:7">
       <c r="A275" s="16" t="s">
         <v>213</v>
       </c>
@@ -6427,7 +6429,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="276" spans="1:7" s="10" customFormat="1">
+    <row r="276" spans="1:7">
       <c r="A276" s="16" t="s">
         <v>213</v>
       </c>
@@ -6444,7 +6446,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="277" spans="1:7" s="10" customFormat="1">
+    <row r="277" spans="1:7">
       <c r="A277" s="16" t="s">
         <v>213</v>
       </c>
@@ -6461,7 +6463,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="278" spans="1:7" s="10" customFormat="1">
+    <row r="278" spans="1:7">
       <c r="A278" s="16" t="s">
         <v>213</v>
       </c>
@@ -6478,7 +6480,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="279" spans="1:7" s="10" customFormat="1">
+    <row r="279" spans="1:7">
       <c r="A279" s="16" t="s">
         <v>213</v>
       </c>
@@ -6495,7 +6497,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="280" spans="1:7" s="10" customFormat="1">
+    <row r="280" spans="1:7">
       <c r="A280" s="16" t="s">
         <v>213</v>
       </c>
@@ -6512,7 +6514,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="281" spans="1:7" s="10" customFormat="1">
+    <row r="281" spans="1:7">
       <c r="A281" s="16" t="s">
         <v>213</v>
       </c>
@@ -6529,7 +6531,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="282" spans="1:7" s="10" customFormat="1">
+    <row r="282" spans="1:7">
       <c r="A282" s="16" t="s">
         <v>213</v>
       </c>
@@ -6546,7 +6548,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="283" spans="1:7" s="10" customFormat="1">
+    <row r="283" spans="1:7">
       <c r="A283" s="16" t="s">
         <v>213</v>
       </c>
@@ -6563,7 +6565,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="284" spans="1:7" s="10" customFormat="1">
+    <row r="284" spans="1:7">
       <c r="A284" s="16" t="s">
         <v>213</v>
       </c>
@@ -6580,7 +6582,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="285" spans="1:7" s="10" customFormat="1">
+    <row r="285" spans="1:7">
       <c r="A285" s="16" t="s">
         <v>213</v>
       </c>
@@ -6597,7 +6599,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="286" spans="1:7" s="10" customFormat="1">
+    <row r="286" spans="1:7">
       <c r="A286" s="16" t="s">
         <v>213</v>
       </c>
@@ -6614,7 +6616,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="287" spans="1:7" s="10" customFormat="1">
+    <row r="287" spans="1:7">
       <c r="A287" s="16" t="s">
         <v>213</v>
       </c>
@@ -6631,7 +6633,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="288" spans="1:7" s="10" customFormat="1">
+    <row r="288" spans="1:7">
       <c r="A288" s="16" t="s">
         <v>213</v>
       </c>
@@ -6648,7 +6650,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="289" spans="1:7" s="10" customFormat="1">
+    <row r="289" spans="1:7">
       <c r="A289" s="16" t="s">
         <v>213</v>
       </c>
@@ -6665,7 +6667,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="290" spans="1:7" s="10" customFormat="1">
+    <row r="290" spans="1:7">
       <c r="A290" s="16" t="s">
         <v>213</v>
       </c>
@@ -6682,7 +6684,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="291" spans="1:7" s="10" customFormat="1">
+    <row r="291" spans="1:7">
       <c r="A291" s="16" t="s">
         <v>213</v>
       </c>
@@ -6699,7 +6701,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="292" spans="1:7" s="10" customFormat="1">
+    <row r="292" spans="1:7">
       <c r="A292" s="16" t="s">
         <v>213</v>
       </c>
@@ -6716,7 +6718,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="293" spans="1:7" s="10" customFormat="1">
+    <row r="293" spans="1:7">
       <c r="A293" s="16" t="s">
         <v>213</v>
       </c>
@@ -6733,7 +6735,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="294" spans="1:7" s="10" customFormat="1">
+    <row r="294" spans="1:7">
       <c r="A294" s="16" t="s">
         <v>213</v>
       </c>
@@ -6750,7 +6752,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="295" spans="1:7" s="10" customFormat="1">
+    <row r="295" spans="1:7">
       <c r="A295" s="16" t="s">
         <v>213</v>
       </c>
@@ -6767,7 +6769,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="296" spans="1:7" s="10" customFormat="1">
+    <row r="296" spans="1:7">
       <c r="A296" s="16" t="s">
         <v>213</v>
       </c>
@@ -6784,7 +6786,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="297" spans="1:7" s="10" customFormat="1">
+    <row r="297" spans="1:7">
       <c r="A297" s="16" t="s">
         <v>213</v>
       </c>
@@ -6801,7 +6803,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="298" spans="1:7" s="10" customFormat="1">
+    <row r="298" spans="1:7">
       <c r="A298" s="16" t="s">
         <v>213</v>
       </c>
@@ -6818,7 +6820,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="299" spans="1:7" s="10" customFormat="1">
+    <row r="299" spans="1:7">
       <c r="A299" s="16" t="s">
         <v>213</v>
       </c>
@@ -6835,7 +6837,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="300" spans="1:7" s="10" customFormat="1">
+    <row r="300" spans="1:7">
       <c r="A300" s="16" t="s">
         <v>213</v>
       </c>
@@ -6852,7 +6854,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="301" spans="1:7" s="10" customFormat="1">
+    <row r="301" spans="1:7">
       <c r="A301" s="16" t="s">
         <v>213</v>
       </c>
@@ -6869,7 +6871,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="302" spans="1:7" s="10" customFormat="1">
+    <row r="302" spans="1:7">
       <c r="A302" s="16" t="s">
         <v>213</v>
       </c>
@@ -6886,7 +6888,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="303" spans="1:7" s="10" customFormat="1">
+    <row r="303" spans="1:7">
       <c r="A303" s="16" t="s">
         <v>213</v>
       </c>
@@ -6903,7 +6905,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="304" spans="1:7" s="10" customFormat="1">
+    <row r="304" spans="1:7">
       <c r="A304" s="16" t="s">
         <v>213</v>
       </c>
@@ -6920,7 +6922,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="305" spans="1:7" s="10" customFormat="1">
+    <row r="305" spans="1:7">
       <c r="A305" s="16" t="s">
         <v>213</v>
       </c>
@@ -6937,7 +6939,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="306" spans="1:7" s="10" customFormat="1">
+    <row r="306" spans="1:7">
       <c r="A306" s="16" t="s">
         <v>213</v>
       </c>
@@ -6954,7 +6956,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="307" spans="1:7" s="10" customFormat="1">
+    <row r="307" spans="1:7">
       <c r="A307" s="16" t="s">
         <v>213</v>
       </c>
@@ -6971,7 +6973,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="308" spans="1:7" s="10" customFormat="1">
+    <row r="308" spans="1:7">
       <c r="A308" s="16" t="s">
         <v>213</v>
       </c>
@@ -6988,7 +6990,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="309" spans="1:7" s="10" customFormat="1">
+    <row r="309" spans="1:7">
       <c r="A309" s="16" t="s">
         <v>213</v>
       </c>
@@ -7005,7 +7007,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="310" spans="1:7" s="10" customFormat="1">
+    <row r="310" spans="1:7">
       <c r="A310" s="16" t="s">
         <v>213</v>
       </c>
@@ -7022,7 +7024,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="311" spans="1:7" s="10" customFormat="1">
+    <row r="311" spans="1:7">
       <c r="A311" s="16" t="s">
         <v>213</v>
       </c>
@@ -7039,7 +7041,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="312" spans="1:7" s="10" customFormat="1">
+    <row r="312" spans="1:7">
       <c r="A312" s="16" t="s">
         <v>213</v>
       </c>
@@ -7056,7 +7058,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="313" spans="1:7" s="10" customFormat="1">
+    <row r="313" spans="1:7">
       <c r="A313" s="16" t="s">
         <v>213</v>
       </c>
@@ -7073,7 +7075,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="314" spans="1:7" s="10" customFormat="1">
+    <row r="314" spans="1:7">
       <c r="A314" s="16" t="s">
         <v>213</v>
       </c>
@@ -7090,7 +7092,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="315" spans="1:7" s="10" customFormat="1">
+    <row r="315" spans="1:7">
       <c r="A315" s="16" t="s">
         <v>213</v>
       </c>
@@ -7107,7 +7109,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="316" spans="1:7" s="10" customFormat="1">
+    <row r="316" spans="1:7">
       <c r="A316" s="16" t="s">
         <v>213</v>
       </c>
@@ -7124,7 +7126,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="317" spans="1:7" s="10" customFormat="1">
+    <row r="317" spans="1:7">
       <c r="A317" s="16" t="s">
         <v>213</v>
       </c>
@@ -7141,7 +7143,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="318" spans="1:7" s="10" customFormat="1">
+    <row r="318" spans="1:7">
       <c r="A318" s="16" t="s">
         <v>213</v>
       </c>
@@ -7158,7 +7160,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="319" spans="1:7" s="10" customFormat="1">
+    <row r="319" spans="1:7">
       <c r="A319" s="16" t="s">
         <v>213</v>
       </c>
@@ -7175,7 +7177,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="320" spans="1:7" s="10" customFormat="1">
+    <row r="320" spans="1:7">
       <c r="A320" s="16"/>
       <c r="B320" s="16"/>
       <c r="C320" s="17"/>
@@ -7184,7 +7186,7 @@
       <c r="F320" s="16"/>
       <c r="G320" s="16"/>
     </row>
-    <row r="321" spans="1:7" s="10" customFormat="1">
+    <row r="321" spans="1:7">
       <c r="A321" s="16" t="s">
         <v>214</v>
       </c>
@@ -7204,7 +7206,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="322" spans="1:7" s="10" customFormat="1">
+    <row r="322" spans="1:7">
       <c r="A322" s="16" t="s">
         <v>214</v>
       </c>
@@ -7224,7 +7226,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="323" spans="1:7" s="10" customFormat="1">
+    <row r="323" spans="1:7">
       <c r="A323" s="16" t="s">
         <v>214</v>
       </c>
@@ -7244,7 +7246,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="324" spans="1:7" s="10" customFormat="1">
+    <row r="324" spans="1:7">
       <c r="A324" s="16" t="s">
         <v>214</v>
       </c>
@@ -7264,7 +7266,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="325" spans="1:7" s="10" customFormat="1">
+    <row r="325" spans="1:7">
       <c r="A325" s="16" t="s">
         <v>214</v>
       </c>
@@ -7284,7 +7286,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="326" spans="1:7" s="10" customFormat="1">
+    <row r="326" spans="1:7">
       <c r="A326" s="16" t="s">
         <v>214</v>
       </c>
@@ -7304,7 +7306,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="327" spans="1:7" s="10" customFormat="1">
+    <row r="327" spans="1:7">
       <c r="A327" s="16" t="s">
         <v>214</v>
       </c>
@@ -7324,7 +7326,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="328" spans="1:7" s="10" customFormat="1">
+    <row r="328" spans="1:7">
       <c r="A328" s="16" t="s">
         <v>214</v>
       </c>
@@ -7344,7 +7346,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="329" spans="1:7" s="10" customFormat="1">
+    <row r="329" spans="1:7">
       <c r="A329" s="16" t="s">
         <v>214</v>
       </c>
@@ -7364,7 +7366,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="330" spans="1:7" s="10" customFormat="1">
+    <row r="330" spans="1:7">
       <c r="A330" s="16" t="s">
         <v>214</v>
       </c>
@@ -7384,7 +7386,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="331" spans="1:7" s="10" customFormat="1">
+    <row r="331" spans="1:7">
       <c r="A331" s="16" t="s">
         <v>214</v>
       </c>
@@ -7404,7 +7406,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="332" spans="1:7" s="10" customFormat="1">
+    <row r="332" spans="1:7">
       <c r="A332" s="16" t="s">
         <v>214</v>
       </c>
@@ -7424,7 +7426,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="333" spans="1:7" s="10" customFormat="1">
+    <row r="333" spans="1:7">
       <c r="A333" s="16" t="s">
         <v>214</v>
       </c>
@@ -7444,7 +7446,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="334" spans="1:7" s="10" customFormat="1">
+    <row r="334" spans="1:7">
       <c r="A334" s="16" t="s">
         <v>214</v>
       </c>
@@ -7464,7 +7466,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="335" spans="1:7" s="10" customFormat="1">
+    <row r="335" spans="1:7">
       <c r="A335" s="16" t="s">
         <v>214</v>
       </c>
@@ -7484,7 +7486,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="336" spans="1:7" s="10" customFormat="1">
+    <row r="336" spans="1:7">
       <c r="A336" s="16" t="s">
         <v>214</v>
       </c>
@@ -7504,7 +7506,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="337" spans="1:7" s="10" customFormat="1">
+    <row r="337" spans="1:7">
       <c r="A337" s="16" t="s">
         <v>214</v>
       </c>
@@ -7524,7 +7526,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="338" spans="1:7" s="10" customFormat="1">
+    <row r="338" spans="1:7">
       <c r="A338" s="16" t="s">
         <v>214</v>
       </c>
@@ -7544,7 +7546,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="339" spans="1:7" s="10" customFormat="1">
+    <row r="339" spans="1:7">
       <c r="A339" s="16" t="s">
         <v>214</v>
       </c>
@@ -7564,7 +7566,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="340" spans="1:7" s="10" customFormat="1">
+    <row r="340" spans="1:7">
       <c r="A340" s="16" t="s">
         <v>214</v>
       </c>
@@ -7584,7 +7586,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="341" spans="1:7" s="10" customFormat="1">
+    <row r="341" spans="1:7">
       <c r="A341" s="16" t="s">
         <v>214</v>
       </c>
@@ -7604,7 +7606,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="342" spans="1:7" s="10" customFormat="1">
+    <row r="342" spans="1:7">
       <c r="A342" s="16" t="s">
         <v>214</v>
       </c>
@@ -7624,7 +7626,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="343" spans="1:7" s="10" customFormat="1">
+    <row r="343" spans="1:7">
       <c r="A343" s="16" t="s">
         <v>214</v>
       </c>
@@ -7644,7 +7646,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="344" spans="1:7" s="10" customFormat="1">
+    <row r="344" spans="1:7">
       <c r="A344" s="16" t="s">
         <v>214</v>
       </c>
@@ -7664,7 +7666,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="345" spans="1:7" s="10" customFormat="1">
+    <row r="345" spans="1:7">
       <c r="A345" s="16" t="s">
         <v>214</v>
       </c>
@@ -7684,7 +7686,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="346" spans="1:7" s="10" customFormat="1">
+    <row r="346" spans="1:7">
       <c r="A346" s="16" t="s">
         <v>214</v>
       </c>
@@ -7704,7 +7706,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="347" spans="1:7" s="10" customFormat="1">
+    <row r="347" spans="1:7">
       <c r="A347" s="16" t="s">
         <v>214</v>
       </c>
@@ -7724,7 +7726,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="348" spans="1:7" s="10" customFormat="1">
+    <row r="348" spans="1:7">
       <c r="A348" s="16" t="s">
         <v>214</v>
       </c>
@@ -7744,7 +7746,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="349" spans="1:7" s="10" customFormat="1">
+    <row r="349" spans="1:7">
       <c r="A349" s="16" t="s">
         <v>214</v>
       </c>
@@ -7764,7 +7766,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="350" spans="1:7" s="10" customFormat="1">
+    <row r="350" spans="1:7">
       <c r="A350" s="16" t="s">
         <v>214</v>
       </c>
@@ -7784,7 +7786,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="351" spans="1:7" s="10" customFormat="1">
+    <row r="351" spans="1:7">
       <c r="A351" s="16" t="s">
         <v>214</v>
       </c>
@@ -7804,7 +7806,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="352" spans="1:7" s="10" customFormat="1">
+    <row r="352" spans="1:7">
       <c r="A352" s="16" t="s">
         <v>214</v>
       </c>
@@ -7824,7 +7826,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="353" spans="1:7" s="10" customFormat="1">
+    <row r="353" spans="1:7">
       <c r="A353" s="16" t="s">
         <v>214</v>
       </c>
@@ -7844,7 +7846,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="354" spans="1:7" s="10" customFormat="1">
+    <row r="354" spans="1:7">
       <c r="A354" s="16" t="s">
         <v>214</v>
       </c>
@@ -7864,7 +7866,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="355" spans="1:7" s="10" customFormat="1">
+    <row r="355" spans="1:7">
       <c r="A355" s="16" t="s">
         <v>214</v>
       </c>
@@ -7884,7 +7886,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="356" spans="1:7" s="10" customFormat="1">
+    <row r="356" spans="1:7">
       <c r="A356" s="16" t="s">
         <v>214</v>
       </c>
@@ -7904,7 +7906,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="357" spans="1:7" s="10" customFormat="1">
+    <row r="357" spans="1:7">
       <c r="A357" s="16" t="s">
         <v>214</v>
       </c>
@@ -7924,7 +7926,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="358" spans="1:7" s="10" customFormat="1">
+    <row r="358" spans="1:7">
       <c r="A358" s="16" t="s">
         <v>214</v>
       </c>
@@ -7944,7 +7946,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="359" spans="1:7" s="10" customFormat="1">
+    <row r="359" spans="1:7">
       <c r="A359" s="16" t="s">
         <v>214</v>
       </c>
@@ -7964,7 +7966,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="360" spans="1:7" s="10" customFormat="1">
+    <row r="360" spans="1:7">
       <c r="A360" s="16" t="s">
         <v>214</v>
       </c>
@@ -7984,7 +7986,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="361" spans="1:7" s="10" customFormat="1">
+    <row r="361" spans="1:7">
       <c r="A361" s="16" t="s">
         <v>214</v>
       </c>
@@ -8004,7 +8006,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="362" spans="1:7" s="10" customFormat="1">
+    <row r="362" spans="1:7">
       <c r="A362" s="16" t="s">
         <v>214</v>
       </c>
@@ -8024,7 +8026,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="363" spans="1:7" s="10" customFormat="1">
+    <row r="363" spans="1:7">
       <c r="A363" s="16" t="s">
         <v>214</v>
       </c>
@@ -8044,7 +8046,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="364" spans="1:7" s="10" customFormat="1">
+    <row r="364" spans="1:7">
       <c r="A364" s="16" t="s">
         <v>214</v>
       </c>
@@ -8064,7 +8066,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="365" spans="1:7" s="10" customFormat="1">
+    <row r="365" spans="1:7">
       <c r="A365" s="16" t="s">
         <v>214</v>
       </c>
@@ -8084,7 +8086,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="366" spans="1:7" s="10" customFormat="1">
+    <row r="366" spans="1:7">
       <c r="A366" s="16" t="s">
         <v>214</v>
       </c>
@@ -8104,7 +8106,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="367" spans="1:7" s="10" customFormat="1">
+    <row r="367" spans="1:7">
       <c r="A367" s="16" t="s">
         <v>214</v>
       </c>
@@ -8124,7 +8126,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="368" spans="1:7" s="10" customFormat="1">
+    <row r="368" spans="1:7">
       <c r="A368" s="16" t="s">
         <v>214</v>
       </c>
@@ -8144,7 +8146,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="369" spans="1:7" s="10" customFormat="1">
+    <row r="369" spans="1:7">
       <c r="A369" s="16" t="s">
         <v>214</v>
       </c>
@@ -8164,7 +8166,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="370" spans="1:7" s="10" customFormat="1">
+    <row r="370" spans="1:7">
       <c r="A370" s="16" t="s">
         <v>214</v>
       </c>
@@ -8184,7 +8186,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="371" spans="1:7" s="10" customFormat="1">
+    <row r="371" spans="1:7">
       <c r="A371" s="16" t="s">
         <v>214</v>
       </c>
@@ -8204,7 +8206,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="372" spans="1:7" s="10" customFormat="1">
+    <row r="372" spans="1:7">
       <c r="A372" s="16" t="s">
         <v>214</v>
       </c>
@@ -8224,7 +8226,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="373" spans="1:7" s="10" customFormat="1">
+    <row r="373" spans="1:7">
       <c r="A373" s="16" t="s">
         <v>214</v>
       </c>
@@ -8244,7 +8246,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="374" spans="1:7" s="10" customFormat="1">
+    <row r="374" spans="1:7">
       <c r="A374" s="16" t="s">
         <v>214</v>
       </c>
@@ -8264,7 +8266,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="375" spans="1:7" s="10" customFormat="1">
+    <row r="375" spans="1:7">
       <c r="A375" s="16" t="s">
         <v>214</v>
       </c>
@@ -8284,7 +8286,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="376" spans="1:7" s="10" customFormat="1">
+    <row r="376" spans="1:7">
       <c r="A376" s="16" t="s">
         <v>214</v>
       </c>
@@ -8304,7 +8306,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="377" spans="1:7" s="10" customFormat="1">
+    <row r="377" spans="1:7">
       <c r="A377" s="16" t="s">
         <v>214</v>
       </c>
@@ -8324,7 +8326,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="378" spans="1:7" s="10" customFormat="1">
+    <row r="378" spans="1:7">
       <c r="A378" s="16" t="s">
         <v>214</v>
       </c>
@@ -8344,7 +8346,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="379" spans="1:7" s="10" customFormat="1">
+    <row r="379" spans="1:7">
       <c r="A379" s="16" t="s">
         <v>214</v>
       </c>
@@ -8364,7 +8366,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="380" spans="1:7" s="10" customFormat="1">
+    <row r="380" spans="1:7">
       <c r="A380" s="16" t="s">
         <v>214</v>
       </c>
@@ -8384,7 +8386,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="381" spans="1:7" s="10" customFormat="1">
+    <row r="381" spans="1:7">
       <c r="A381" s="16" t="s">
         <v>214</v>
       </c>
@@ -8404,7 +8406,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="382" spans="1:7" s="10" customFormat="1">
+    <row r="382" spans="1:7">
       <c r="A382" s="16" t="s">
         <v>214</v>
       </c>
@@ -8424,7 +8426,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="383" spans="1:7" s="10" customFormat="1">
+    <row r="383" spans="1:7">
       <c r="A383" s="16" t="s">
         <v>214</v>
       </c>
@@ -8444,7 +8446,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="384" spans="1:7" s="10" customFormat="1">
+    <row r="384" spans="1:7">
       <c r="A384" s="16" t="s">
         <v>214</v>
       </c>
@@ -8464,7 +8466,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="385" spans="1:7" s="10" customFormat="1">
+    <row r="385" spans="1:7">
       <c r="A385" s="16" t="s">
         <v>214</v>
       </c>
@@ -8484,7 +8486,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="386" spans="1:7" s="10" customFormat="1">
+    <row r="386" spans="1:7">
       <c r="A386" s="16" t="s">
         <v>214</v>
       </c>
@@ -8504,7 +8506,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="387" spans="1:7" s="10" customFormat="1">
+    <row r="387" spans="1:7">
       <c r="A387" s="16" t="s">
         <v>214</v>
       </c>
@@ -8524,7 +8526,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="388" spans="1:7" s="10" customFormat="1">
+    <row r="388" spans="1:7">
       <c r="A388" s="16" t="s">
         <v>214</v>
       </c>
@@ -8544,7 +8546,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="389" spans="1:7" s="10" customFormat="1">
+    <row r="389" spans="1:7">
       <c r="A389" s="16" t="s">
         <v>214</v>
       </c>
@@ -8564,7 +8566,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="390" spans="1:7" s="10" customFormat="1">
+    <row r="390" spans="1:7">
       <c r="A390" s="16" t="s">
         <v>214</v>
       </c>
@@ -8584,7 +8586,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="391" spans="1:7" s="10" customFormat="1">
+    <row r="391" spans="1:7">
       <c r="A391" s="16" t="s">
         <v>214</v>
       </c>
@@ -8604,7 +8606,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="392" spans="1:7" s="10" customFormat="1">
+    <row r="392" spans="1:7">
       <c r="A392" s="16" t="s">
         <v>214</v>
       </c>
@@ -8624,7 +8626,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="393" spans="1:7" s="10" customFormat="1">
+    <row r="393" spans="1:7">
       <c r="A393" s="16" t="s">
         <v>214</v>
       </c>
@@ -8644,7 +8646,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="394" spans="1:7" s="10" customFormat="1">
+    <row r="394" spans="1:7">
       <c r="A394" s="16" t="s">
         <v>214</v>
       </c>
@@ -8664,7 +8666,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="395" spans="1:7" s="10" customFormat="1">
+    <row r="395" spans="1:7">
       <c r="A395" s="16" t="s">
         <v>214</v>
       </c>
@@ -8684,7 +8686,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="396" spans="1:7" s="10" customFormat="1">
+    <row r="396" spans="1:7">
       <c r="A396" s="16" t="s">
         <v>214</v>
       </c>
@@ -8704,7 +8706,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="397" spans="1:7" s="10" customFormat="1">
+    <row r="397" spans="1:7">
       <c r="A397" s="16" t="s">
         <v>214</v>
       </c>
@@ -8724,7 +8726,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="398" spans="1:7" s="10" customFormat="1">
+    <row r="398" spans="1:7">
       <c r="A398" s="16" t="s">
         <v>214</v>
       </c>
@@ -8744,7 +8746,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="399" spans="1:7" s="10" customFormat="1">
+    <row r="399" spans="1:7">
       <c r="A399" s="16" t="s">
         <v>214</v>
       </c>
@@ -8764,7 +8766,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="400" spans="1:7" s="10" customFormat="1">
+    <row r="400" spans="1:7">
       <c r="A400" s="16" t="s">
         <v>214</v>
       </c>
@@ -8784,7 +8786,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="401" spans="1:7" s="10" customFormat="1">
+    <row r="401" spans="1:7">
       <c r="A401" s="16" t="s">
         <v>214</v>
       </c>
@@ -8804,7 +8806,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="402" spans="1:7" s="10" customFormat="1">
+    <row r="402" spans="1:7">
       <c r="A402" s="16" t="s">
         <v>214</v>
       </c>
@@ -8824,7 +8826,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="403" spans="1:7" s="10" customFormat="1">
+    <row r="403" spans="1:7">
       <c r="A403" s="16" t="s">
         <v>214</v>
       </c>
@@ -8844,7 +8846,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="404" spans="1:7" s="10" customFormat="1">
+    <row r="404" spans="1:7">
       <c r="A404" s="16" t="s">
         <v>214</v>
       </c>
@@ -8864,7 +8866,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="405" spans="1:7" s="10" customFormat="1">
+    <row r="405" spans="1:7">
       <c r="A405" s="16" t="s">
         <v>214</v>
       </c>
@@ -8884,7 +8886,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="406" spans="1:7" s="10" customFormat="1">
+    <row r="406" spans="1:7">
       <c r="A406" s="16" t="s">
         <v>214</v>
       </c>
@@ -8904,7 +8906,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="407" spans="1:7" s="10" customFormat="1">
+    <row r="407" spans="1:7">
       <c r="A407" s="16" t="s">
         <v>214</v>
       </c>
@@ -8924,7 +8926,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="408" spans="1:7" s="10" customFormat="1">
+    <row r="408" spans="1:7">
       <c r="A408" s="16" t="s">
         <v>214</v>
       </c>
@@ -8944,7 +8946,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="409" spans="1:7" s="10" customFormat="1">
+    <row r="409" spans="1:7">
       <c r="A409" s="16" t="s">
         <v>214</v>
       </c>
@@ -8964,7 +8966,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="410" spans="1:7" s="10" customFormat="1">
+    <row r="410" spans="1:7">
       <c r="A410" s="16" t="s">
         <v>214</v>
       </c>
@@ -8984,7 +8986,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="411" spans="1:7" s="10" customFormat="1">
+    <row r="411" spans="1:7">
       <c r="A411" s="16" t="s">
         <v>214</v>
       </c>
@@ -9004,7 +9006,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="412" spans="1:7" s="10" customFormat="1">
+    <row r="412" spans="1:7">
       <c r="A412" s="16" t="s">
         <v>214</v>
       </c>
@@ -9024,7 +9026,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="413" spans="1:7" s="10" customFormat="1">
+    <row r="413" spans="1:7">
       <c r="A413" s="16" t="s">
         <v>214</v>
       </c>
@@ -9044,7 +9046,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="414" spans="1:7" s="10" customFormat="1">
+    <row r="414" spans="1:7">
       <c r="A414" s="16" t="s">
         <v>214</v>
       </c>
@@ -9064,7 +9066,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="415" spans="1:7" s="10" customFormat="1">
+    <row r="415" spans="1:7">
       <c r="A415" s="16" t="s">
         <v>214</v>
       </c>
@@ -9084,7 +9086,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="416" spans="1:7" s="10" customFormat="1">
+    <row r="416" spans="1:7">
       <c r="A416" s="16" t="s">
         <v>214</v>
       </c>
@@ -9104,7 +9106,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="417" spans="1:7" s="10" customFormat="1">
+    <row r="417" spans="1:7">
       <c r="A417" s="16" t="s">
         <v>214</v>
       </c>
@@ -9124,7 +9126,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="418" spans="1:7" s="10" customFormat="1">
+    <row r="418" spans="1:7">
       <c r="A418" s="16" t="s">
         <v>214</v>
       </c>
@@ -9144,7 +9146,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="419" spans="1:7" s="10" customFormat="1">
+    <row r="419" spans="1:7">
       <c r="A419" s="16" t="s">
         <v>214</v>
       </c>
@@ -9164,7 +9166,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="420" spans="1:7" s="10" customFormat="1">
+    <row r="420" spans="1:7">
       <c r="A420" s="16" t="s">
         <v>214</v>
       </c>
